--- a/tools/importer/reports/import-directory-breadcrumb.report.xlsx
+++ b/tools/importer/reports/import-directory-breadcrumb.report.xlsx
@@ -52,7 +52,7 @@
     <t>section-landing-hero-cards</t>
   </si>
   <si>
-    <t>2026-06-12T20:22:25.162Z</t>
+    <t>2026-06-13T17:56:08.440Z</t>
   </si>
   <si>
     <t>About Banner Health | Leading Nonprofit Health System</t>
@@ -73,7 +73,7 @@
     <t>search-listing</t>
   </si>
   <si>
-    <t>2026-06-12T20:23:24.393Z</t>
+    <t>2026-06-13T17:57:04.270Z</t>
   </si>
   <si>
     <t>Calendar of Events | Banner Health</t>
@@ -91,7 +91,7 @@
     <t>careers</t>
   </si>
   <si>
-    <t>2026-06-12T20:22:30.709Z</t>
+    <t>2026-06-13T17:56:14.170Z</t>
   </si>
   <si>
     <t>Health Care Careers</t>
@@ -109,7 +109,7 @@
     <t>contact-us</t>
   </si>
   <si>
-    <t>2026-06-12T20:23:29.173Z</t>
+    <t>2026-06-13T17:57:10.277Z</t>
   </si>
   <si>
     <t>Contact Us | Banner Health</t>
@@ -127,7 +127,7 @@
     <t>getcarenow</t>
   </si>
   <si>
-    <t>2026-06-12T20:22:53.270Z</t>
+    <t>2026-06-13T17:56:37.918Z</t>
   </si>
   <si>
     <t>Obtenga atención ahora | Banner Health</t>
@@ -145,7 +145,7 @@
     <t>health-professionals</t>
   </si>
   <si>
-    <t>2026-06-12T20:22:58.958Z</t>
+    <t>2026-06-13T17:56:42.763Z</t>
   </si>
   <si>
     <t>Para Profesionales de la Salud</t>
@@ -160,7 +160,7 @@
     <t>healthcareblog</t>
   </si>
   <si>
-    <t>2026-06-12T20:23:53.623Z</t>
+    <t>2026-06-13T17:57:33.285Z</t>
   </si>
   <si>
     <t>Banner Health Blog</t>
@@ -181,7 +181,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-12T20:22:16.298Z</t>
+    <t>2026-06-13T17:56:02.540Z</t>
   </si>
   <si>
     <t>Banner Health | Health Care Made Easier in AZ, CO, WY, NE, NV, CA</t>
@@ -196,7 +196,7 @@
     <t>insurance</t>
   </si>
   <si>
-    <t>2026-06-12T20:23:04.793Z</t>
+    <t>2026-06-13T17:56:47.788Z</t>
   </si>
   <si>
     <t>Planes y redes Banner | Banner Health</t>
@@ -217,7 +217,7 @@
     <t>breadcrumb-partner-content</t>
   </si>
   <si>
-    <t>2026-06-12T20:24:38.292Z</t>
+    <t>2026-06-13T17:58:30.137Z</t>
   </si>
   <si>
     <t>Kaiser Permanenete | Banner Health</t>
@@ -235,7 +235,7 @@
     <t>locations</t>
   </si>
   <si>
-    <t>2026-06-12T20:23:19.554Z</t>
+    <t>2026-06-13T17:56:58.070Z</t>
   </si>
   <si>
     <t>Our Locations | Banner Health</t>
@@ -253,7 +253,7 @@
     <t>medicare</t>
   </si>
   <si>
-    <t>2026-06-12T20:24:01.268Z</t>
+    <t>2026-06-13T17:57:39.124Z</t>
   </si>
   <si>
     <t>Banner Medicare</t>
@@ -274,7 +274,7 @@
     <t>cards-landing</t>
   </si>
   <si>
-    <t>2026-06-12T20:24:51.841Z</t>
+    <t>2026-06-13T17:58:41.927Z</t>
   </si>
   <si>
     <t>Banner Network Colorado</t>
@@ -292,7 +292,7 @@
     <t>networksouth</t>
   </si>
   <si>
-    <t>2026-06-12T20:24:07.134Z</t>
+    <t>2026-06-13T17:57:45.591Z</t>
   </si>
   <si>
     <t>Banner Network Southern Arizona</t>
@@ -307,7 +307,7 @@
     <t>newsroom</t>
   </si>
   <si>
-    <t>2026-06-12T20:24:14.980Z</t>
+    <t>2026-06-13T17:57:52.876Z</t>
   </si>
   <si>
     <t>Banner Health | Newsroom and Media Resource Center</t>
@@ -325,7 +325,7 @@
     <t>physician-directory</t>
   </si>
   <si>
-    <t>2026-06-12T20:09:57.871Z</t>
+    <t>2026-06-13T17:20:26.802Z</t>
   </si>
   <si>
     <t>Find a Doctor</t>
@@ -340,7 +340,7 @@
     <t>search-results</t>
   </si>
   <si>
-    <t>2026-06-12T20:09:01.982Z</t>
+    <t>2026-06-13T17:20:32.734Z</t>
   </si>
   <si>
     <t>Banner Health Search Results | Banner Health</t>
@@ -358,7 +358,7 @@
     <t>hero-landing</t>
   </si>
   <si>
-    <t>2026-06-12T20:21:51.186Z</t>
+    <t>2026-06-13T17:58:18.326Z</t>
   </si>
   <si>
     <t>Services</t>
@@ -373,7 +373,7 @@
     <t>staying-well</t>
   </si>
   <si>
-    <t>2026-06-12T20:23:09.983Z</t>
+    <t>2026-06-13T17:56:52.423Z</t>
   </si>
   <si>
     <t>Ayúdame a estar bien | Banner Health</t>
@@ -388,7 +388,7 @@
     <t>es/about</t>
   </si>
   <si>
-    <t>2026-06-12T20:22:36.349Z</t>
+    <t>2026-06-13T17:56:19.733Z</t>
   </si>
   <si>
     <t>Acerca de Banner Health | Sistema líder de salud sin fines de lucro</t>
@@ -403,7 +403,7 @@
     <t>es/calendar</t>
   </si>
   <si>
-    <t>2026-06-12T20:23:35.652Z</t>
+    <t>2026-06-13T17:57:17.187Z</t>
   </si>
   <si>
     <t>Calendario de Eventos | Banner Health</t>
@@ -418,7 +418,7 @@
     <t>es/careers</t>
   </si>
   <si>
-    <t>2026-06-12T20:22:42.362Z</t>
+    <t>2026-06-13T17:56:25.415Z</t>
   </si>
   <si>
     <t>Carreras de atención médica</t>
@@ -433,7 +433,7 @@
     <t>es/contact-us</t>
   </si>
   <si>
-    <t>2026-06-12T20:23:40.878Z</t>
+    <t>2026-06-13T17:57:22.304Z</t>
   </si>
   <si>
     <t>Contáctenos | Banner Health</t>
@@ -451,7 +451,7 @@
     <t>breadcrumb-content</t>
   </si>
   <si>
-    <t>2026-06-12T20:10:06.210Z</t>
+    <t>2026-06-13T17:34:43.159Z</t>
   </si>
   <si>
     <t>https://www.bannerhealth.com/es/getcarenow</t>
@@ -469,7 +469,7 @@
     <t>service-detail-cards-carousel</t>
   </si>
   <si>
-    <t>2026-06-12T20:24:29.542Z</t>
+    <t>2026-06-13T17:58:12.695Z</t>
   </si>
   <si>
     <t>Blog de Banner Health</t>
@@ -484,7 +484,7 @@
     <t>es/kaiser-permanente</t>
   </si>
   <si>
-    <t>2026-06-12T20:24:42.991Z</t>
+    <t>2026-06-13T17:58:36.349Z</t>
   </si>
   <si>
     <t>Káiser Permanente | Banner Health</t>
@@ -499,7 +499,7 @@
     <t>es/locations</t>
   </si>
   <si>
-    <t>2026-06-12T20:23:47.637Z</t>
+    <t>2026-06-13T17:57:28.357Z</t>
   </si>
   <si>
     <t>Nuestras Ubicaciones | Banner Health</t>
@@ -514,7 +514,7 @@
     <t>es/medicare</t>
   </si>
   <si>
-    <t>2026-06-12T20:24:24.934Z</t>
+    <t>2026-06-13T17:58:07.541Z</t>
   </si>
   <si>
     <t>https://www.bannerhealth.com/es/medicare</t>
@@ -529,7 +529,7 @@
     <t>directory-breadcrumb</t>
   </si>
   <si>
-    <t>2026-06-12T20:25:00.171Z</t>
+    <t>2026-06-13T17:58:46.645Z</t>
   </si>
   <si>
     <t>Encuentre un médico</t>
@@ -544,7 +544,7 @@
     <t>es/search-results</t>
   </si>
   <si>
-    <t>2026-06-12T20:09:08.403Z</t>
+    <t>2026-06-13T17:34:48.850Z</t>
   </si>
   <si>
     <t>Resultados de la búsqueda de Banner Health | Banner Health</t>
@@ -559,7 +559,7 @@
     <t>es/services</t>
   </si>
   <si>
-    <t>2026-06-12T20:21:57.157Z</t>
+    <t>2026-06-13T17:58:25.038Z</t>
   </si>
   <si>
     <t>Servicios</t>
@@ -574,7 +574,7 @@
     <t>es/staying-well</t>
   </si>
   <si>
-    <t>2026-06-12T20:22:47.235Z</t>
+    <t>2026-06-13T17:56:31.441Z</t>
   </si>
   <si>
     <t>https://www.bannerhealth.com/es/staying-well</t>
